--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E447FE-CB06-4597-A438-604791B3D1AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07F817F-2AAB-4D22-A0CC-71FBE3F01869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <author>William Crowe</author>
   </authors>
   <commentList>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{29A9FAE4-E562-48D1-898F-AACF01903855}">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{29A9FAE4-E562-48D1-898F-AACF01903855}">
       <text>
         <r>
           <rPr>
@@ -50,7 +50,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="N6" authorId="0" shapeId="0" xr:uid="{15D9EEE2-CA5C-43BC-8B01-BAD97442DCCA}">
+    <comment ref="N6" authorId="0" shapeId="0" xr:uid="{BCE5732D-8DBC-45D3-AD06-DE6C52058431}">
+      <text/>
+    </comment>
+    <comment ref="N9" authorId="0" shapeId="0" xr:uid="{15D9EEE2-CA5C-43BC-8B01-BAD97442DCCA}">
       <text>
         <r>
           <rPr>
@@ -58,7 +61,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>William Crowe:</t>
         </r>
@@ -67,17 +70,17 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 ag</t>
         </r>
       </text>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{CA909996-4AD5-4A8E-BC32-A84A0EF3DC22}">
+    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{CA909996-4AD5-4A8E-BC32-A84A0EF3DC22}">
       <text/>
     </comment>
-    <comment ref="N11" authorId="0" shapeId="0" xr:uid="{EA1A2A5E-A06B-40B8-AD76-10A0C357D3D9}">
+    <comment ref="N13" authorId="0" shapeId="0" xr:uid="{EA1A2A5E-A06B-40B8-AD76-10A0C357D3D9}">
       <text>
         <r>
           <rPr>
@@ -85,19 +88,19 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>William Cro</t>
         </r>
       </text>
     </comment>
-    <comment ref="N12" authorId="0" shapeId="0" xr:uid="{CDFEB8DC-D67E-4B6C-8EDB-0209B7067E46}">
+    <comment ref="N14" authorId="0" shapeId="0" xr:uid="{CDFEB8DC-D67E-4B6C-8EDB-0209B7067E46}">
       <text/>
     </comment>
-    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{42DD0172-6C19-48BB-B243-CCA7486AD89C}">
+    <comment ref="K15" authorId="0" shapeId="0" xr:uid="{42DD0172-6C19-48BB-B243-CCA7486AD89C}">
       <text/>
     </comment>
-    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{70B6D392-BBF5-4F37-A24C-C6D0CB98E777}">
+    <comment ref="K16" authorId="0" shapeId="0" xr:uid="{70B6D392-BBF5-4F37-A24C-C6D0CB98E777}">
       <text>
         <r>
           <rPr>
@@ -105,7 +108,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>William Crowe:</t>
         </r>
@@ -114,14 +117,14 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="K16" authorId="0" shapeId="0" xr:uid="{1FD260F4-F1C1-4801-BDA5-7AB52B8FF343}">
+    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{1FD260F4-F1C1-4801-BDA5-7AB52B8FF343}">
       <text>
         <r>
           <rPr>
@@ -145,10 +148,10 @@
         </r>
       </text>
     </comment>
-    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{27ED2F2B-6702-43E5-8352-44F7B654D995}">
+    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{27ED2F2B-6702-43E5-8352-44F7B654D995}">
       <text/>
     </comment>
-    <comment ref="N18" authorId="0" shapeId="0" xr:uid="{E563512F-E421-48EF-A838-552E02BD8306}">
+    <comment ref="N20" authorId="0" shapeId="0" xr:uid="{E563512F-E421-48EF-A838-552E02BD8306}">
       <text>
         <r>
           <rPr>
@@ -156,16 +159,16 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>William Crow</t>
         </r>
       </text>
     </comment>
-    <comment ref="N19" authorId="0" shapeId="0" xr:uid="{B0CF4723-74B5-407C-A895-E1C19159F65D}">
+    <comment ref="N21" authorId="0" shapeId="0" xr:uid="{B0CF4723-74B5-407C-A895-E1C19159F65D}">
       <text/>
     </comment>
-    <comment ref="N22" authorId="0" shapeId="0" xr:uid="{FF7BB13A-1F8C-455B-A5E7-FE64CDF23808}">
+    <comment ref="N24" authorId="0" shapeId="0" xr:uid="{FF7BB13A-1F8C-455B-A5E7-FE64CDF23808}">
       <text/>
     </comment>
   </commentList>
@@ -173,7 +176,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="230">
   <si>
     <t>section</t>
   </si>
@@ -211,9 +214,6 @@
     <t>The Deanery School</t>
   </si>
   <si>
-    <t>wyfc.magic@gmail.com</t>
-  </si>
-  <si>
     <t>Wichelstowe Sports Hub</t>
   </si>
   <si>
@@ -256,9 +256,6 @@
     <t>Chris Blackwell</t>
   </si>
   <si>
-    <t>wyfc.warriors@gmail.com</t>
-  </si>
-  <si>
     <t>Panthers</t>
   </si>
   <si>
@@ -268,9 +265,6 @@
     <t>Thursday 18:00</t>
   </si>
   <si>
-    <t>wyfc.panthers@gmail.com</t>
-  </si>
-  <si>
     <t>Warriors is a team for boys and girls, playing in the North Wilts Youth Football U12 Division 5 League</t>
   </si>
   <si>
@@ -283,9 +277,6 @@
     <t>Tuesday evenings</t>
   </si>
   <si>
-    <t xml:space="preserve">	wyfc.rhinos@gmail.com</t>
-  </si>
-  <si>
     <t>Blackcats</t>
   </si>
   <si>
@@ -295,27 +286,18 @@
     <t>Tuesdays 18:00</t>
   </si>
   <si>
-    <t>wyfc.blackcats@gmail.com</t>
-  </si>
-  <si>
     <t>Rams</t>
   </si>
   <si>
     <t>Lisa Coe &amp; Adam Rutter</t>
   </si>
   <si>
-    <t>wyfc.rams@gmail.com</t>
-  </si>
-  <si>
     <t>Rangers</t>
   </si>
   <si>
     <t>Stuart Beggs</t>
   </si>
   <si>
-    <t>wyfc.rangers01@gmail.com</t>
-  </si>
-  <si>
     <t>Tuesdays 17.30</t>
   </si>
   <si>
@@ -325,9 +307,6 @@
     <t>Dave Salter</t>
   </si>
   <si>
-    <t>wyfc.rockets@gmail.com</t>
-  </si>
-  <si>
     <t>Thursday evenings</t>
   </si>
   <si>
@@ -337,9 +316,6 @@
     <t>Martin Speakman</t>
   </si>
   <si>
-    <t>wyfc.dragons@gmail.com</t>
-  </si>
-  <si>
     <t>Lightning</t>
   </si>
   <si>
@@ -349,15 +325,9 @@
     <t>Lightning is a team for boys and girls, playing in the North Wilts Youth Football U11 Development Purple League</t>
   </si>
   <si>
-    <t>wyfc.lightning@gmail.com</t>
-  </si>
-  <si>
     <t>Foxes</t>
   </si>
   <si>
-    <t>wyfc.foxes@gmail.com</t>
-  </si>
-  <si>
     <t>Thunder</t>
   </si>
   <si>
@@ -367,36 +337,24 @@
     <t>Paul Whitewood</t>
   </si>
   <si>
-    <t>wyfc.thunder@gmail.com</t>
-  </si>
-  <si>
     <t>Wookies</t>
   </si>
   <si>
     <t>Scott Bailey</t>
   </si>
   <si>
-    <t>wyfc.wookies@gmail.com</t>
-  </si>
-  <si>
     <t>Witches</t>
   </si>
   <si>
     <t>Chris Burridge</t>
   </si>
   <si>
-    <t>wyfc.witches@gmail.com</t>
-  </si>
-  <si>
     <t>Wrens</t>
   </si>
   <si>
     <t>Chris Burridge &amp; Natasha Burridge</t>
   </si>
   <si>
-    <t>wyfc.wrens@gmail.com</t>
-  </si>
-  <si>
     <t>Ravens</t>
   </si>
   <si>
@@ -424,9 +382,6 @@
     <t>The Rangers are a team for boys and girls, playing in the North Wilts Youth Football U9 Development Green League</t>
   </si>
   <si>
-    <t>wyfc.ravens@gmail.com</t>
-  </si>
-  <si>
     <t>Mens</t>
   </si>
   <si>
@@ -439,9 +394,6 @@
     <t>The Men's team is a senior team playing in the Swindon and District Community Football League</t>
   </si>
   <si>
-    <t>wyfc.chair@gmail.com</t>
-  </si>
-  <si>
     <t>tbc</t>
   </si>
   <si>
@@ -463,18 +415,12 @@
     <t>Tuesday Evenings</t>
   </si>
   <si>
-    <t>wyfc.lions@gmail.com</t>
-  </si>
-  <si>
     <t>Wasps</t>
   </si>
   <si>
     <t>Reece Kewley &amp; Jack Kewley</t>
   </si>
   <si>
-    <t>wyfc.wasps@gmail.com</t>
-  </si>
-  <si>
     <t>Wolves</t>
   </si>
   <si>
@@ -484,9 +430,6 @@
     <t>Monday Evenings</t>
   </si>
   <si>
-    <t>wyfc.wolves@gmail.com</t>
-  </si>
-  <si>
     <t>Hurricanes</t>
   </si>
   <si>
@@ -496,18 +439,12 @@
     <t>Wednesday Evenings</t>
   </si>
   <si>
-    <t>wyfc.hurricanes@gmail.com</t>
-  </si>
-  <si>
     <t>Tornadoes</t>
   </si>
   <si>
     <t>Darren Harvey</t>
   </si>
   <si>
-    <t>wyfc.tornadoes@gmail.com</t>
-  </si>
-  <si>
     <t>Silverbacks</t>
   </si>
   <si>
@@ -517,18 +454,12 @@
     <t>Thursday Evenings</t>
   </si>
   <si>
-    <t>wyfc.silverbacks@gmail.com</t>
-  </si>
-  <si>
     <t>Broncos</t>
   </si>
   <si>
     <t>Rob Zukovic</t>
   </si>
   <si>
-    <t>wyfc.broncos@gmail.com</t>
-  </si>
-  <si>
     <t>u18</t>
   </si>
   <si>
@@ -536,9 +467,6 @@
   </si>
   <si>
     <t>The Under 18 is a team for young people, playing in the North Wilts Youth Football U17/18 Division 1 League</t>
-  </si>
-  <si>
-    <t>wroughtonyouthfc@gmail.com</t>
   </si>
   <si>
     <t>The Panthers are a team for boys and girls playing in the North Wilts FA Red Development League</t>
@@ -862,12 +790,117 @@
       <t>We're real people who live and breathe property, design, and doing things differently. Independent, unapologetic, and full of fresh perspective, we're a team of visionaries, lettings pros, creatives and developers who see beyond the usual.</t>
     </r>
   </si>
+  <si>
+    <t>Black Cats</t>
+  </si>
+  <si>
+    <t>Jamie Pidgeon</t>
+  </si>
+  <si>
+    <t>blackcats@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>wroughtonyouthfc@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>magic@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>panthers@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>rhinos@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>rams@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>rangers@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>rockets@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>dragons@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>lightning@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>foxes@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>thunder@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>wookies@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>warriors@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>witches@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>wrens@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>ravens@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>clubsecretary_adult@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>lions@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>wasps@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>wolves@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>hurricanes@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>tornadoes@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>silverbacks@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>broncos@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>Mens Sunday League team, playing in the Swindon Sunday Football League</t>
+  </si>
+  <si>
+    <t>Mens - Sumday League</t>
+  </si>
+  <si>
+    <t>Rebels</t>
+  </si>
+  <si>
+    <t>Jack Morement</t>
+  </si>
+  <si>
+    <t>The Rebels are a newly formed team, starting at u8 and playing 5v5 Footnall</t>
+  </si>
+  <si>
+    <t>rebels@wwfc.org.uk</t>
+  </si>
+  <si>
+    <t>/images/sponsors/rebels.png</t>
+  </si>
+  <si>
+    <t>/images/teams/rebels/rebels.jpg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1065,19 +1098,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1444,7 +1464,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -1480,18 +1500,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1869,7 +1892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52D2363D-25C8-4F80-BF49-26CC19A643F2}">
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.77734375" customWidth="1"/>
@@ -1917,36 +1940,36 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="K1" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="L1" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="M1" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="N1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="69" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>196</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -1955,42 +1978,24 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K2" t="s">
-        <v>136</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="M2" t="s">
-        <v>137</v>
-      </c>
-      <c r="N2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
       <c r="B3">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>195</v>
       </c>
       <c r="D3" t="s">
-        <v>196</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>132</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -1998,506 +2003,502 @@
       <c r="G3" t="b">
         <v>1</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="I3" t="s">
-        <v>12</v>
+      <c r="H3" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="J3" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="K3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>129</v>
+        <v>111</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="M3" t="s">
+        <v>112</v>
       </c>
       <c r="N3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>107</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>122</v>
+      <c r="H4" s="4" t="s">
+        <v>106</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="10"/>
+        <v>199</v>
+      </c>
+      <c r="J4" t="s">
+        <v>114</v>
+      </c>
+      <c r="K4" t="s">
+        <v>105</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="N4" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5">
+        <v>2018</v>
+      </c>
+      <c r="C5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="K5" t="s">
+        <v>228</v>
+      </c>
+      <c r="L5" s="9"/>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6">
         <v>2017</v>
       </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6">
-        <v>2016</v>
-      </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>124</v>
+      <c r="H6" s="3" t="s">
+        <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>43</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="L6" s="10"/>
       <c r="N6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="I7" t="s">
-        <v>46</v>
+        <v>98</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="N7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="42" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>125</v>
+      <c r="H8" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>50</v>
+        <v>202</v>
+      </c>
+      <c r="N8" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>54</v>
+        <v>203</v>
       </c>
       <c r="N9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" t="s">
-        <v>150</v>
-      </c>
-      <c r="K10" t="s">
-        <v>149</v>
-      </c>
-      <c r="L10" t="s">
-        <v>151</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="N10" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>2014</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>204</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="J11" t="s">
-        <v>200</v>
-      </c>
-      <c r="K11" t="s">
-        <v>201</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>203</v>
+        <v>66</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>205</v>
       </c>
       <c r="N11" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12">
         <v>2014</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>62</v>
+      <c r="H12" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>64</v>
+        <v>206</v>
+      </c>
+      <c r="J12" t="s">
+        <v>125</v>
+      </c>
+      <c r="K12" t="s">
+        <v>124</v>
+      </c>
+      <c r="L12" t="s">
+        <v>126</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="N12" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>179</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>67</v>
+      <c r="H13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>207</v>
       </c>
       <c r="J13" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="K13" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>199</v>
+        <v>177</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="N13" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="45" x14ac:dyDescent="0.7">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="1">
-        <v>19</v>
+        <v>52</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="N14" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15">
+        <v>2013</v>
+      </c>
+      <c r="C15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J14" t="s">
-        <v>164</v>
-      </c>
-      <c r="K14" t="s">
-        <v>171</v>
-      </c>
-      <c r="L14" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="N14" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15">
-        <v>2012</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>70</v>
+        <v>209</v>
       </c>
       <c r="J15" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K15" t="s">
-        <v>148</v>
-      </c>
-      <c r="L15" t="s">
-        <v>146</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="N15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="45" x14ac:dyDescent="0.7">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B16">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
+      </c>
+      <c r="E16" s="1">
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
-      <c r="H16" s="7" t="s">
-        <v>76</v>
+      <c r="H16" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="J16" t="s">
+        <v>139</v>
+      </c>
+      <c r="K16" t="s">
+        <v>146</v>
+      </c>
+      <c r="L16" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="K16" t="s">
+      <c r="M16" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="L16" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="N16" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2505,16 +2506,16 @@
         <v>9</v>
       </c>
       <c r="B17">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
@@ -2523,80 +2524,83 @@
         <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>83</v>
+        <v>211</v>
       </c>
       <c r="J17" t="s">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="K17" t="s">
-        <v>168</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="M17" t="s">
-        <v>170</v>
-      </c>
-      <c r="N17" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="64.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="L17" t="s">
+        <v>121</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="B18">
+        <v>2010</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>88</v>
+        <v>212</v>
       </c>
       <c r="J18" t="s">
-        <v>208</v>
+        <v>115</v>
       </c>
       <c r="K18" t="s">
-        <v>205</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="M18" t="s">
-        <v>207</v>
+        <v>116</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="N18" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>2010</v>
       </c>
       <c r="C19" t="s">
-        <v>193</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>89</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
@@ -2604,358 +2608,457 @@
       <c r="G19" t="b">
         <v>1</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>194</v>
+      <c r="H19" s="7" t="s">
+        <v>62</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
+      </c>
+      <c r="J19" t="s">
+        <v>142</v>
+      </c>
+      <c r="K19" t="s">
+        <v>143</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="M19" t="s">
+        <v>145</v>
       </c>
       <c r="N19" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="64.8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>92</v>
+      <c r="H20" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>12</v>
+        <v>214</v>
       </c>
       <c r="J20" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="K20" t="s">
-        <v>191</v>
-      </c>
-      <c r="L20" s="18"/>
-      <c r="M20" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="M20" t="s">
+        <v>182</v>
+      </c>
+      <c r="N20" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B21">
-        <v>2012</v>
-      </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="D21" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L21" s="17" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+      <c r="N21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
-        <v>2012</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="F22" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
-      <c r="H22" s="7" t="s">
-        <v>210</v>
+      <c r="H22" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="J22" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="K22" t="s">
-        <v>172</v>
-      </c>
-      <c r="N22" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+      <c r="L22" s="18"/>
+      <c r="M22" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23">
         <v>2012</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J23" t="s">
-        <v>140</v>
-      </c>
-      <c r="K23" t="s">
-        <v>141</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="M23" t="s">
-        <v>142</v>
-      </c>
-      <c r="N23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>213</v>
+      <c r="H24" s="7" t="s">
+        <v>185</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>107</v>
+        <v>216</v>
       </c>
       <c r="J24" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="K24" t="s">
-        <v>153</v>
-      </c>
-      <c r="L24" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="N24" t="s">
         <v>159</v>
       </c>
-      <c r="M24" t="s">
-        <v>155</v>
-      </c>
-      <c r="N24" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25">
+        <v>2012</v>
+      </c>
+      <c r="C25" t="s">
+        <v>81</v>
+      </c>
+      <c r="D25" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="J25" t="s">
+        <v>115</v>
+      </c>
+      <c r="K25" t="s">
+        <v>116</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="M25" t="s">
+        <v>117</v>
+      </c>
+      <c r="N25" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26">
         <v>2011</v>
       </c>
-      <c r="C25" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F25" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="L25" s="14"/>
-      <c r="N25" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26">
-        <v>2010</v>
-      </c>
       <c r="C26" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L26" s="14"/>
-    </row>
-    <row r="27" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+      <c r="J26" t="s">
+        <v>129</v>
+      </c>
+      <c r="K26" t="s">
+        <v>128</v>
+      </c>
+      <c r="L26" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="M26" t="s">
+        <v>130</v>
+      </c>
+      <c r="N26" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="D27" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="F27" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G27" t="b">
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>216</v>
+        <v>189</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="L27" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="L27" s="14"/>
+      <c r="N27" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B28">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="C28" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>120</v>
+      <c r="H28" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="J28" t="s">
-        <v>157</v>
-      </c>
-      <c r="K28" t="s">
-        <v>160</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="M28" t="s">
+        <v>220</v>
+      </c>
+      <c r="L28" s="14"/>
+    </row>
+    <row r="29" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29">
+        <v>2009</v>
+      </c>
+      <c r="C29" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="L29" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30">
+        <v>2007</v>
+      </c>
+      <c r="C30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="J30" t="s">
+        <v>132</v>
+      </c>
+      <c r="K30" t="s">
+        <v>135</v>
+      </c>
+      <c r="L30" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="M30" t="s">
+        <v>133</v>
+      </c>
+      <c r="N30" t="s">
         <v>158</v>
       </c>
-      <c r="N28" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="E29" s="1"/>
-      <c r="L29" s="14"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="E31" s="1"/>
+    </row>
+    <row r="31" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" t="s">
+        <v>223</v>
+      </c>
+      <c r="D31" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="L31" s="14"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="E32" s="1"/>
@@ -3080,41 +3183,54 @@
     <row r="72" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E72" s="1"/>
     </row>
+    <row r="73" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E73" s="1"/>
+    </row>
+    <row r="74" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E74" s="1"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I14" r:id="rId1" xr:uid="{1DDE6441-190C-4FB5-88D6-BD2305EF1037}"/>
-    <hyperlink ref="I4" r:id="rId2" xr:uid="{464AEA72-DD90-493F-B1EA-F064D72E58ED}"/>
-    <hyperlink ref="I6" r:id="rId3" xr:uid="{C3FB2965-268C-4260-B12A-BF3B3D06E0D2}"/>
-    <hyperlink ref="I8" r:id="rId4" display="mailto:wyfc.rockets@gmail.com" xr:uid="{94AEF066-47C6-4A5E-810B-679E732621D3}"/>
-    <hyperlink ref="I9" r:id="rId5" display="mailto:wyfc.dragons@gmail.com" xr:uid="{1199F452-4FFD-4443-A221-CB874C056106}"/>
-    <hyperlink ref="I10" r:id="rId6" display="mailto:wyfc.lightning@gmail.com" xr:uid="{45D87601-135B-4938-9E30-D9DBAB839D74}"/>
-    <hyperlink ref="I12" r:id="rId7" xr:uid="{F964898C-E695-43AF-ABF1-6B2AEEF41DA5}"/>
-    <hyperlink ref="I13" r:id="rId8" xr:uid="{A277BAD3-7950-4856-83E2-B3B805CDE7FB}"/>
-    <hyperlink ref="I15" r:id="rId9" xr:uid="{4FFCD438-A697-4E2B-862E-AEB7FBA70D2C}"/>
-    <hyperlink ref="I16" r:id="rId10" xr:uid="{ACE97416-41EF-4E1A-9C81-891544793CCB}"/>
-    <hyperlink ref="I17" r:id="rId11" xr:uid="{F740E58B-F83F-407C-8A2A-205A90C20C2B}"/>
-    <hyperlink ref="I18" r:id="rId12" xr:uid="{C1A06EC3-1156-4297-856C-F9D31C5D8517}"/>
-    <hyperlink ref="I19" r:id="rId13" xr:uid="{A83EFAE6-7C65-4944-B61E-D63B500BFEC2}"/>
-    <hyperlink ref="I20" r:id="rId14" xr:uid="{D586C23B-DE62-4E2A-A1BE-6E6679A289EE}"/>
-    <hyperlink ref="I21" r:id="rId15" xr:uid="{0CC4A010-A755-4529-B3BC-88360D529C8F}"/>
-    <hyperlink ref="I22" r:id="rId16" xr:uid="{66D5CA7C-D658-4136-9E90-8186A7EC0D49}"/>
-    <hyperlink ref="I23" r:id="rId17" xr:uid="{EB731D00-8BAD-493A-B65D-D9FDCB99DA24}"/>
-    <hyperlink ref="I24" r:id="rId18" xr:uid="{FB09940C-8366-4603-B0B9-5A7F0FE53856}"/>
-    <hyperlink ref="I25" r:id="rId19" xr:uid="{1F0DF1FE-3341-4D07-9881-D7032C2BCFD6}"/>
-    <hyperlink ref="I26" r:id="rId20" xr:uid="{34FD123B-32E2-4723-A99F-B214EF856113}"/>
-    <hyperlink ref="I27" r:id="rId21" xr:uid="{1DA03B7F-3218-4DA3-89B0-AEB5BF3B2793}"/>
-    <hyperlink ref="I28" r:id="rId22" xr:uid="{9A40DF52-6BA2-4984-9B40-763FAC09DA40}"/>
-    <hyperlink ref="M3" r:id="rId23" xr:uid="{41620B85-57B4-4EA1-83B0-0EC365818842}"/>
-    <hyperlink ref="M15" r:id="rId24" xr:uid="{334F4A00-D252-43DB-BCCF-7E0762FE4D0A}"/>
-    <hyperlink ref="M10" r:id="rId25" xr:uid="{923F8D44-DFAD-4DE1-8022-AAA409E43920}"/>
-    <hyperlink ref="M16" r:id="rId26" xr:uid="{80BF0B3C-6F43-4D23-98BE-97C5F752891C}"/>
-    <hyperlink ref="M14" r:id="rId27" xr:uid="{9F723FE9-2235-4D80-B338-C2273BDEA705}"/>
-    <hyperlink ref="M20" r:id="rId28" xr:uid="{38A395C6-5484-4F9A-89D4-25C7597D6F80}"/>
-    <hyperlink ref="M11" r:id="rId29" xr:uid="{77B1CEF9-89D1-4450-B781-5912FF963AF3}"/>
+    <hyperlink ref="I16" r:id="rId1" xr:uid="{1DDE6441-190C-4FB5-88D6-BD2305EF1037}"/>
+    <hyperlink ref="I6" r:id="rId2" xr:uid="{464AEA72-DD90-493F-B1EA-F064D72E58ED}"/>
+    <hyperlink ref="I8" r:id="rId3" xr:uid="{C3FB2965-268C-4260-B12A-BF3B3D06E0D2}"/>
+    <hyperlink ref="I10" r:id="rId4" xr:uid="{94AEF066-47C6-4A5E-810B-679E732621D3}"/>
+    <hyperlink ref="I11" r:id="rId5" xr:uid="{1199F452-4FFD-4443-A221-CB874C056106}"/>
+    <hyperlink ref="I12" r:id="rId6" xr:uid="{45D87601-135B-4938-9E30-D9DBAB839D74}"/>
+    <hyperlink ref="I14" r:id="rId7" xr:uid="{F964898C-E695-43AF-ABF1-6B2AEEF41DA5}"/>
+    <hyperlink ref="I15" r:id="rId8" xr:uid="{A277BAD3-7950-4856-83E2-B3B805CDE7FB}"/>
+    <hyperlink ref="I17" r:id="rId9" xr:uid="{4FFCD438-A697-4E2B-862E-AEB7FBA70D2C}"/>
+    <hyperlink ref="I18" r:id="rId10" xr:uid="{ACE97416-41EF-4E1A-9C81-891544793CCB}"/>
+    <hyperlink ref="I19" r:id="rId11" xr:uid="{F740E58B-F83F-407C-8A2A-205A90C20C2B}"/>
+    <hyperlink ref="I20" r:id="rId12" xr:uid="{C1A06EC3-1156-4297-856C-F9D31C5D8517}"/>
+    <hyperlink ref="I21" r:id="rId13" xr:uid="{A83EFAE6-7C65-4944-B61E-D63B500BFEC2}"/>
+    <hyperlink ref="I22" r:id="rId14" xr:uid="{D586C23B-DE62-4E2A-A1BE-6E6679A289EE}"/>
+    <hyperlink ref="I23" r:id="rId15" xr:uid="{0CC4A010-A755-4529-B3BC-88360D529C8F}"/>
+    <hyperlink ref="I24" r:id="rId16" xr:uid="{66D5CA7C-D658-4136-9E90-8186A7EC0D49}"/>
+    <hyperlink ref="I25" r:id="rId17" xr:uid="{EB731D00-8BAD-493A-B65D-D9FDCB99DA24}"/>
+    <hyperlink ref="I26" r:id="rId18" xr:uid="{FB09940C-8366-4603-B0B9-5A7F0FE53856}"/>
+    <hyperlink ref="I27" r:id="rId19" xr:uid="{1F0DF1FE-3341-4D07-9881-D7032C2BCFD6}"/>
+    <hyperlink ref="I28" r:id="rId20" xr:uid="{34FD123B-32E2-4723-A99F-B214EF856113}"/>
+    <hyperlink ref="I29" r:id="rId21" xr:uid="{1DA03B7F-3218-4DA3-89B0-AEB5BF3B2793}"/>
+    <hyperlink ref="I30" r:id="rId22" display="wroughtonyouthfc@gmail.com" xr:uid="{9A40DF52-6BA2-4984-9B40-763FAC09DA40}"/>
+    <hyperlink ref="M4" r:id="rId23" xr:uid="{41620B85-57B4-4EA1-83B0-0EC365818842}"/>
+    <hyperlink ref="M17" r:id="rId24" xr:uid="{334F4A00-D252-43DB-BCCF-7E0762FE4D0A}"/>
+    <hyperlink ref="M12" r:id="rId25" xr:uid="{923F8D44-DFAD-4DE1-8022-AAA409E43920}"/>
+    <hyperlink ref="M18" r:id="rId26" xr:uid="{80BF0B3C-6F43-4D23-98BE-97C5F752891C}"/>
+    <hyperlink ref="M16" r:id="rId27" xr:uid="{9F723FE9-2235-4D80-B338-C2273BDEA705}"/>
+    <hyperlink ref="M22" r:id="rId28" xr:uid="{38A395C6-5484-4F9A-89D4-25C7597D6F80}"/>
+    <hyperlink ref="M13" r:id="rId29" xr:uid="{77B1CEF9-89D1-4450-B781-5912FF963AF3}"/>
+    <hyperlink ref="I3" r:id="rId30" xr:uid="{8FBC3070-57A5-4643-BD91-89139673F939}"/>
+    <hyperlink ref="I4" r:id="rId31" xr:uid="{FF057201-A735-481C-BBE0-E336E8585596}"/>
+    <hyperlink ref="I7" r:id="rId32" xr:uid="{45A95AEE-91F7-4E4A-8790-9E500E4E86BC}"/>
+    <hyperlink ref="I9" r:id="rId33" xr:uid="{2FE118A7-FE9F-4A6F-8070-4D4AB117119B}"/>
+    <hyperlink ref="I13" r:id="rId34" xr:uid="{74EE51BD-5E7D-437E-AC27-795A6775677B}"/>
+    <hyperlink ref="I31" r:id="rId35" xr:uid="{0E34F95B-DB9B-4185-B354-C94C4E2CC368}"/>
+    <hyperlink ref="I5" r:id="rId36" xr:uid="{1599383C-8599-4B21-8BFD-1E77CE910E68}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId30"/>
-  <legacyDrawing r:id="rId31"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId37"/>
+  <legacyDrawing r:id="rId38"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
@@ -3122,7 +3238,7 @@
           <x14:formula1>
             <xm:f>data!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>F18:F1048576 I7 F1:F16</xm:sqref>
+          <xm:sqref>F20:F1048576 F1:F18</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FA1CACC6-E1C6-4D34-9880-2BA45F8D9BBE}">
           <x14:formula1>
@@ -3173,10 +3289,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>2000</v>
@@ -3187,10 +3303,10 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3">
         <v>2001</v>
@@ -3212,10 +3328,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>2003</v>
@@ -3223,10 +3339,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>2004</v>
@@ -3234,10 +3350,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7">
         <v>2005</v>
@@ -3245,7 +3361,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8">
         <v>2006</v>
@@ -3253,7 +3369,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9">
         <v>2007</v>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C07F817F-2AAB-4D22-A0CC-71FBE3F01869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B77F19-BA5F-49AF-AFB4-74C53003A4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -47,33 +47,6 @@
           </rPr>
           <t xml:space="preserve">
 </t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N6" authorId="0" shapeId="0" xr:uid="{BCE5732D-8DBC-45D3-AD06-DE6C52058431}">
-      <text/>
-    </comment>
-    <comment ref="N9" authorId="0" shapeId="0" xr:uid="{15D9EEE2-CA5C-43BC-8B01-BAD97442DCCA}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>William Crowe:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-ag</t>
         </r>
       </text>
     </comment>
@@ -1986,7 +1959,7 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C3" t="s">
         <v>195</v>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B77F19-BA5F-49AF-AFB4-74C53003A4FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1B45A8-69D6-486C-989E-F529F2CFEF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -149,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="229">
   <si>
     <t>section</t>
   </si>
@@ -861,9 +861,6 @@
   </si>
   <si>
     <t>rebels@wwfc.org.uk</t>
-  </si>
-  <si>
-    <t>/images/sponsors/rebels.png</t>
   </si>
   <si>
     <t>/images/teams/rebels/rebels.jpg</t>
@@ -1933,7 +1930,7 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
@@ -2071,7 +2068,7 @@
         <v>227</v>
       </c>
       <c r="K5" t="s">
-        <v>228</v>
+        <v>105</v>
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="2"/>
@@ -2106,7 +2103,7 @@
       </c>
       <c r="L6" s="10"/>
       <c r="N6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E1B45A8-69D6-486C-989E-F529F2CFEF93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA0DCF6-556A-4B5C-A0DC-E0AAD7B47925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -26,30 +26,6 @@
     <author>William Crowe</author>
   </authors>
   <commentList>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{29A9FAE4-E562-48D1-898F-AACF01903855}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>William Crowe:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="K13" authorId="0" shapeId="0" xr:uid="{CA909996-4AD5-4A8E-BC32-A84A0EF3DC22}">
       <text/>
     </comment>
@@ -149,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="231">
   <si>
     <t>section</t>
   </si>
@@ -864,6 +840,12 @@
   </si>
   <si>
     <t>/images/teams/rebels/rebels.jpg</t>
+  </si>
+  <si>
+    <t>/images/sponsors/blackcats.png</t>
+  </si>
+  <si>
+    <t>A new u7 girls team, formed in 2026.	 If your daughter would would like to be considered for a trial, please register your interest via the email address below.</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1416,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
@@ -1470,7 +1452,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1485,6 +1466,12 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1948,7 +1935,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>109</v>
+        <v>230</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="K2" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="55.2" x14ac:dyDescent="0.3">
@@ -2029,7 +2022,7 @@
       <c r="K4" t="s">
         <v>105</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="21" t="s">
         <v>118</v>
       </c>
       <c r="M4" s="2" t="s">
@@ -2335,7 +2328,7 @@
       <c r="H13" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="19" t="s">
         <v>207</v>
       </c>
       <c r="J13" t="s">
@@ -2344,7 +2337,7 @@
       <c r="K13" t="s">
         <v>176</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="L13" s="15" t="s">
         <v>177</v>
       </c>
       <c r="M13" s="2" t="s">
@@ -2420,14 +2413,14 @@
       <c r="K15" t="s">
         <v>173</v>
       </c>
-      <c r="L15" s="16" t="s">
+      <c r="L15" s="15" t="s">
         <v>174</v>
       </c>
       <c r="N15" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="45" x14ac:dyDescent="0.7">
+    <row r="16" spans="1:14" ht="59.4" x14ac:dyDescent="0.7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2461,7 +2454,7 @@
       <c r="K16" t="s">
         <v>146</v>
       </c>
-      <c r="L16" s="15" t="s">
+      <c r="L16" s="20" t="s">
         <v>140</v>
       </c>
       <c r="M16" s="2" t="s">
@@ -2631,7 +2624,7 @@
       <c r="K20" t="s">
         <v>180</v>
       </c>
-      <c r="L20" s="19" t="s">
+      <c r="L20" s="18" t="s">
         <v>194</v>
       </c>
       <c r="M20" t="s">
@@ -2701,7 +2694,7 @@
       <c r="K22" t="s">
         <v>166</v>
       </c>
-      <c r="L22" s="18"/>
+      <c r="L22" s="17"/>
       <c r="M22" s="2" t="s">
         <v>170</v>
       </c>
@@ -2734,7 +2727,7 @@
       <c r="I23" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="L23" s="17" t="s">
+      <c r="L23" s="16" t="s">
         <v>181</v>
       </c>
     </row>
@@ -3197,10 +3190,11 @@
     <hyperlink ref="I13" r:id="rId34" xr:uid="{74EE51BD-5E7D-437E-AC27-795A6775677B}"/>
     <hyperlink ref="I31" r:id="rId35" xr:uid="{0E34F95B-DB9B-4185-B354-C94C4E2CC368}"/>
     <hyperlink ref="I5" r:id="rId36" xr:uid="{1599383C-8599-4B21-8BFD-1E77CE910E68}"/>
+    <hyperlink ref="I2" r:id="rId37" xr:uid="{B1A40085-0039-45D0-968E-37A94CA05EFE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId37"/>
-  <legacyDrawing r:id="rId38"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId38"/>
+  <legacyDrawing r:id="rId39"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBA0DCF6-556A-4B5C-A0DC-E0AAD7B47925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223FD560-9C5B-4EAA-9E7E-3B943F5493D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -1863,7 +1863,7 @@
     <col min="9" max="9" width="29.109375" customWidth="1"/>
     <col min="10" max="10" width="30.33203125" customWidth="1"/>
     <col min="11" max="11" width="35.6640625" customWidth="1"/>
-    <col min="12" max="12" width="84.6640625" customWidth="1"/>
+    <col min="12" max="12" width="37.44140625" customWidth="1"/>
     <col min="13" max="13" width="39.5546875" customWidth="1"/>
     <col min="14" max="14" width="31.88671875" customWidth="1"/>
   </cols>
@@ -2065,6 +2065,9 @@
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="2"/>
+      <c r="N5" t="s">
+        <v>228</v>
+      </c>
     </row>
     <row r="6" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -2096,7 +2099,7 @@
       </c>
       <c r="L6" s="10"/>
       <c r="N6" t="s">
-        <v>228</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
@@ -2128,7 +2131,7 @@
         <v>201</v>
       </c>
       <c r="N7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -2160,7 +2163,7 @@
         <v>202</v>
       </c>
       <c r="N8" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2192,10 +2195,10 @@
         <v>203</v>
       </c>
       <c r="N9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="42" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -2222,9 +2225,6 @@
       </c>
       <c r="I10" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="N10" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
@@ -2303,7 +2303,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="216" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="59.4" x14ac:dyDescent="0.7">
+    <row r="16" spans="1:14" ht="118.8" x14ac:dyDescent="0.7">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="134.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="352.8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="64.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="162" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" ht="216" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="L28" s="14"/>
     </row>
-    <row r="29" spans="1:14" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -3197,7 +3197,7 @@
   <legacyDrawing r:id="rId39"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CB56C8E2-25DC-4AA5-91D7-E5156E468E07}">
           <x14:formula1>
             <xm:f>data!$A$1:$A$9</xm:f>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223FD560-9C5B-4EAA-9E7E-3B943F5493D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E2DD5A-7DB6-4303-948D-4DC73D9BB376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="232">
   <si>
     <t>section</t>
   </si>
@@ -846,6 +846,9 @@
   </si>
   <si>
     <t>A new u7 girls team, formed in 2026.	 If your daughter would would like to be considered for a trial, please register your interest via the email address below.</t>
+  </si>
+  <si>
+    <t>The Rebels</t>
   </si>
 </sst>
 </file>
@@ -2060,6 +2063,9 @@
       <c r="I5" s="2" t="s">
         <v>227</v>
       </c>
+      <c r="J5" t="s">
+        <v>231</v>
+      </c>
       <c r="K5" t="s">
         <v>105</v>
       </c>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32E2DD5A-7DB6-4303-948D-4DC73D9BB376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9987BC-FBA8-4E92-B2D9-73E95149D79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="233">
   <si>
     <t>section</t>
   </si>
@@ -849,6 +849,9 @@
   </si>
   <si>
     <t>The Rebels</t>
+  </si>
+  <si>
+    <t>/images/sponsors/rebels.png</t>
   </si>
 </sst>
 </file>
@@ -2067,7 +2070,7 @@
         <v>231</v>
       </c>
       <c r="K5" t="s">
-        <v>105</v>
+        <v>232</v>
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="2"/>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F9987BC-FBA8-4E92-B2D9-73E95149D79C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73EF3329-516A-455F-A3F4-44A74B4FADA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -214,9 +214,6 @@
     <t>Thursday 18:00</t>
   </si>
   <si>
-    <t>Warriors is a team for boys and girls, playing in the North Wilts Youth Football U12 Division 5 League</t>
-  </si>
-  <si>
     <t>Rhinos</t>
   </si>
   <si>
@@ -271,18 +268,12 @@
     <t>Michaal Webb &amp; Holly Mills</t>
   </si>
   <si>
-    <t>Lightning is a team for boys and girls, playing in the North Wilts Youth Football U11 Development Purple League</t>
-  </si>
-  <si>
     <t>Foxes</t>
   </si>
   <si>
     <t>Thunder</t>
   </si>
   <si>
-    <t>Thunder is a team for boys and girls, playing in the North Wilts Youth Football U11 Development Red League</t>
-  </si>
-  <si>
     <t>Paul Whitewood</t>
   </si>
   <si>
@@ -310,27 +301,6 @@
     <t>Craig Jones &amp; Natasha James</t>
   </si>
   <si>
-    <t>The Wrens are a team for girls, playing in the North Wilts Youth Football U14 Division 5 League</t>
-  </si>
-  <si>
-    <t>The Ravens are a team for girls, playing in the North Wilts Football U14 Division 6 League.</t>
-  </si>
-  <si>
-    <t>The Witches are a team for girls, playing in the North Wilts Youth Football U13 Division 1 Girls League</t>
-  </si>
-  <si>
-    <t>The Wookies are a team for boys and girls, playing in the North Wilts Youth Football U12 Division 2 League</t>
-  </si>
-  <si>
-    <t>The Foxes are a team for boys and girls, playing in the North Wilts Youth Football U11 Development Red League</t>
-  </si>
-  <si>
-    <t>The Dragons are a team for boys and girls, playing in the North Wilts Youth Football U11 Development Blue League</t>
-  </si>
-  <si>
-    <t>The Rangers are a team for boys and girls, playing in the North Wilts Youth Football U9 Development Green League</t>
-  </si>
-  <si>
     <t>Mens</t>
   </si>
   <si>
@@ -340,9 +310,6 @@
     <t>Wednesdays</t>
   </si>
   <si>
-    <t>The Men's team is a senior team playing in the Swindon and District Community Football League</t>
-  </si>
-  <si>
     <t>tbc</t>
   </si>
   <si>
@@ -418,16 +385,7 @@
     <t>The Under 18 is a team for young people, playing in the North Wilts Youth Football U17/18 Division 1 League</t>
   </si>
   <si>
-    <t>The Panthers are a team for boys and girls playing in the North Wilts FA Red Development League</t>
-  </si>
-  <si>
     <t>The Rhinos are a team for boys and girls.</t>
-  </si>
-  <si>
-    <t>The Rams are a team for boys and girls, playing in the North Wilts Youth Football U9 Development Green League</t>
-  </si>
-  <si>
-    <t>The Rockets are a team for boys and girls, playing in the North Wilts Youth Football U10 Development Red League</t>
   </si>
   <si>
     <t>sponsorName</t>
@@ -680,9 +638,6 @@
   </si>
   <si>
     <t>https://www.thefoxwroughton.com/</t>
-  </si>
-  <si>
-    <t>Mehdi  Najafi / Richie Lester</t>
   </si>
   <si>
     <t>/images/sponsors/location.jpg</t>
@@ -852,6 +807,51 @@
   </si>
   <si>
     <t>/images/sponsors/rebels.png</t>
+  </si>
+  <si>
+    <t>Richie Lester</t>
+  </si>
+  <si>
+    <t>The Foxes are a team for boys and girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>Lightning is a team for boys and girls, playing in the North Wilts Youth Football  League</t>
+  </si>
+  <si>
+    <t>The Dragons are a team for boys and girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>Thunder is a team for boys and girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>The Wookies are a team for boys and girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>Warriors is a team for boys and girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>The Witches are a team for girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>The Wrens are a team for girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>The Ravens are a team for girls, playing in the North Wilts Football League.</t>
+  </si>
+  <si>
+    <t>The Men's team is a senior team playing in the Swindon and District Communit League</t>
+  </si>
+  <si>
+    <t>The Panthers are a team for boys and girls playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>The Rams are a team for boys and girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>The Rangers are a team for boys and girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>The Rockets are a team for boys and girls, playing in the North Wilts Youth Football League</t>
   </si>
 </sst>
 </file>
@@ -1903,19 +1903,19 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="K1" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="L1" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="M1" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="N1" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="55.2" x14ac:dyDescent="0.3">
@@ -1926,13 +1926,13 @@
         <v>2019</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -1941,13 +1941,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="K2" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="55.2" x14ac:dyDescent="0.3">
@@ -1958,13 +1958,13 @@
         <v>2017</v>
       </c>
       <c r="C3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -1973,25 +1973,25 @@
         <v>1</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="J3" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="K3" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="M3" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="N3" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
@@ -2005,10 +2005,10 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -2017,25 +2017,25 @@
         <v>1</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="J4" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="K4" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="N4" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="27" x14ac:dyDescent="0.3">
@@ -2046,10 +2046,10 @@
         <v>2018</v>
       </c>
       <c r="C5" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="D5" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>28</v>
@@ -2061,21 +2061,21 @@
         <v>0</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="J5" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="K5" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="2"/>
       <c r="N5" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2101,14 +2101,14 @@
         <v>1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>97</v>
+        <v>229</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="L6" s="10"/>
       <c r="N6" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="28.2" x14ac:dyDescent="0.3">
@@ -2119,13 +2119,13 @@
         <v>2017</v>
       </c>
       <c r="C7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="F7" t="s">
         <v>15</v>
@@ -2134,13 +2134,13 @@
         <v>1</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="N7" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -2151,13 +2151,13 @@
         <v>2016</v>
       </c>
       <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
         <v>36</v>
       </c>
-      <c r="D8" t="s">
-        <v>37</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
@@ -2166,16 +2166,16 @@
         <v>1</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>99</v>
+        <v>230</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="N8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -2183,13 +2183,13 @@
         <v>2016</v>
       </c>
       <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
         <v>38</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="F9" t="s">
         <v>11</v>
@@ -2198,16 +2198,16 @@
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>67</v>
+        <v>231</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="N9" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -2215,13 +2215,13 @@
         <v>2015</v>
       </c>
       <c r="C10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" t="s">
         <v>41</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -2230,13 +2230,13 @@
         <v>1</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -2244,13 +2244,13 @@
         <v>2014</v>
       </c>
       <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
         <v>44</v>
       </c>
-      <c r="D11" t="s">
-        <v>45</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
@@ -2259,16 +2259,16 @@
         <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>66</v>
+        <v>221</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="N11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="55.8" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="42" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -2276,13 +2276,13 @@
         <v>2014</v>
       </c>
       <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
         <v>46</v>
       </c>
-      <c r="D12" t="s">
-        <v>47</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -2291,25 +2291,25 @@
         <v>1</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="J12" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="K12" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="L12" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="N12" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="216" x14ac:dyDescent="0.3">
@@ -2320,13 +2320,13 @@
         <v>2014</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
@@ -2335,25 +2335,25 @@
         <v>1</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>65</v>
+        <v>219</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="J13" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="K13" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -2364,13 +2364,13 @@
         <v>2014</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
@@ -2379,13 +2379,13 @@
         <v>1</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>51</v>
+        <v>222</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="N14" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2396,13 +2396,13 @@
         <v>2013</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -2411,22 +2411,22 @@
         <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>64</v>
+        <v>223</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="J15" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="K15" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="N15" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="118.8" x14ac:dyDescent="0.7">
@@ -2452,25 +2452,25 @@
         <v>1</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>29</v>
+        <v>224</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="J16" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="K16" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="L16" s="20" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="N16" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -2481,13 +2481,13 @@
         <v>2012</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" t="s">
         <v>11</v>
@@ -2496,22 +2496,22 @@
         <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>63</v>
+        <v>225</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="J17" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="K17" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="352.8" x14ac:dyDescent="0.3">
@@ -2522,13 +2522,13 @@
         <v>2010</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F18" t="s">
         <v>11</v>
@@ -2537,25 +2537,25 @@
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>61</v>
+        <v>226</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="J18" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="K18" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="L18" s="12" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="N18" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -2566,13 +2566,13 @@
         <v>2010</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F19" t="s">
         <v>11</v>
@@ -2581,25 +2581,25 @@
         <v>1</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>62</v>
+        <v>227</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="J19" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="K19" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="M19" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="N19" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="162" x14ac:dyDescent="0.3">
@@ -2607,13 +2607,13 @@
         <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
@@ -2622,25 +2622,25 @@
         <v>1</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>71</v>
+        <v>228</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="J20" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="K20" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="M20" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="N20" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -2648,13 +2648,13 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F21" t="s">
         <v>11</v>
@@ -2663,13 +2663,13 @@
         <v>1</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N21" t="s">
         <v>169</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="N21" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -2677,13 +2677,13 @@
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F22" t="s">
         <v>11</v>
@@ -2692,20 +2692,20 @@
         <v>1</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="J22" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="K22" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="L22" s="17"/>
       <c r="M22" s="2" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2716,13 +2716,13 @@
         <v>2012</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F23" t="s">
         <v>18</v>
@@ -2731,13 +2731,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -2748,13 +2748,13 @@
         <v>2012</v>
       </c>
       <c r="C24" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F24" t="s">
         <v>17</v>
@@ -2763,19 +2763,19 @@
         <v>1</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="J24" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="K24" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="N24" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="216" x14ac:dyDescent="0.3">
@@ -2786,13 +2786,13 @@
         <v>2012</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -2801,25 +2801,25 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="J25" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="K25" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="L25" s="13" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="M25" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="N25" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="187.2" x14ac:dyDescent="0.3">
@@ -2830,13 +2830,13 @@
         <v>2011</v>
       </c>
       <c r="C26" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F26" t="s">
         <v>17</v>
@@ -2845,25 +2845,25 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="J26" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="K26" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="L26" s="13" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="M26" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="N26" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2874,13 +2874,13 @@
         <v>2011</v>
       </c>
       <c r="C27" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -2889,14 +2889,14 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="L27" s="14"/>
       <c r="N27" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2907,13 +2907,13 @@
         <v>2010</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -2922,10 +2922,10 @@
         <v>1</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="L28" s="14"/>
     </row>
@@ -2937,13 +2937,13 @@
         <v>2009</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F29" t="s">
         <v>17</v>
@@ -2952,13 +2952,13 @@
         <v>1</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2969,13 +2969,13 @@
         <v>2007</v>
       </c>
       <c r="C30" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -2984,25 +2984,25 @@
         <v>1</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="J30" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="K30" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="M30" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="N30" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -3010,13 +3010,13 @@
         <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="D31" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -3025,10 +3025,10 @@
         <v>1</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="L31" s="14"/>
     </row>
@@ -3206,7 +3206,7 @@
   <legacyDrawing r:id="rId39"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CB56C8E2-25DC-4AA5-91D7-E5156E468E07}">
           <x14:formula1>
             <xm:f>data!$A$1:$A$9</xm:f>

--- a/src/data/teams-master.xlsx
+++ b/src/data/teams-master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\wwfc\wwfc-website\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73EF3329-516A-455F-A3F4-44A74B4FADA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD4DC09-AD80-41A1-9A00-65EFB93FFB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7DF92C9-0D00-4B55-9052-44BB95C1396F}"/>
   </bookViews>
@@ -587,9 +587,6 @@
     <t>/images/teams/wolves/wolves.webp | /images/teams/wolves/wolves.jpg</t>
   </si>
   <si>
-    <t>/images/teams/foxes/foxes.jpg | /images/teams/foxes/foxes1.jpg</t>
-  </si>
-  <si>
     <t>/images/teams/rams/rams.jpg | /images/teams/rams/rrt.jpg</t>
   </si>
   <si>
@@ -852,6 +849,9 @@
   </si>
   <si>
     <t>The Rockets are a team for boys and girls, playing in the North Wilts Youth Football League</t>
+  </si>
+  <si>
+    <t>/images/teams/foxes/foxes new.jpg</t>
   </si>
 </sst>
 </file>
@@ -1929,7 +1929,7 @@
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E2" t="s">
         <v>34</v>
@@ -1941,13 +1941,13 @@
         <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="55.2" x14ac:dyDescent="0.3">
@@ -1958,7 +1958,7 @@
         <v>2017</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -1976,7 +1976,7 @@
         <v>95</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J3" t="s">
         <v>96</v>
@@ -1991,10 +1991,10 @@
         <v>98</v>
       </c>
       <c r="N3" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="66.599999999999994" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>93</v>
@@ -2020,7 +2020,7 @@
         <v>92</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J4" t="s">
         <v>100</v>
@@ -2046,10 +2046,10 @@
         <v>2018</v>
       </c>
       <c r="C5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" t="s">
         <v>209</v>
-      </c>
-      <c r="D5" t="s">
-        <v>210</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>28</v>
@@ -2061,21 +2061,21 @@
         <v>0</v>
       </c>
       <c r="H5" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="J5" t="s">
+        <v>215</v>
+      </c>
+      <c r="K5" t="s">
         <v>216</v>
-      </c>
-      <c r="K5" t="s">
-        <v>217</v>
       </c>
       <c r="L5" s="9"/>
       <c r="M5" s="2"/>
       <c r="N5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2101,10 +2101,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L6" s="10"/>
       <c r="N6" t="s">
@@ -2137,7 +2137,7 @@
         <v>86</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N7" t="s">
         <v>140</v>
@@ -2166,13 +2166,13 @@
         <v>1</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2198,13 +2198,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2230,10 +2230,10 @@
         <v>1</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="42" x14ac:dyDescent="0.3">
@@ -2259,10 +2259,10 @@
         <v>1</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N11" t="s">
         <v>134</v>
@@ -2291,10 +2291,10 @@
         <v>1</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J12" t="s">
         <v>111</v>
@@ -2323,7 +2323,7 @@
         <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>31</v>
@@ -2335,25 +2335,25 @@
         <v>1</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I13" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J13" t="s">
+        <v>160</v>
+      </c>
+      <c r="K13" t="s">
         <v>161</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="L13" s="15" t="s">
+      <c r="M13" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="N13" t="s">
-        <v>148</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -2379,13 +2379,13 @@
         <v>1</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2411,19 +2411,19 @@
         <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J15" t="s">
+        <v>157</v>
+      </c>
+      <c r="K15" t="s">
         <v>158</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" s="15" t="s">
         <v>159</v>
-      </c>
-      <c r="L15" s="15" t="s">
-        <v>160</v>
       </c>
       <c r="N15" t="s">
         <v>139</v>
@@ -2452,10 +2452,10 @@
         <v>1</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J16" t="s">
         <v>125</v>
@@ -2496,10 +2496,10 @@
         <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J17" t="s">
         <v>106</v>
@@ -2537,10 +2537,10 @@
         <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J18" t="s">
         <v>101</v>
@@ -2581,10 +2581,10 @@
         <v>1</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J19" t="s">
         <v>128</v>
@@ -2622,22 +2622,22 @@
         <v>1</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L20" s="18" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N20" t="s">
         <v>143</v>
@@ -2648,7 +2648,7 @@
         <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D21" t="s">
         <v>59</v>
@@ -2663,13 +2663,13 @@
         <v>1</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N21" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="27.6" x14ac:dyDescent="0.3">
@@ -2695,17 +2695,17 @@
         <v>64</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J22" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="L22" s="17"/>
       <c r="M22" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
@@ -2731,13 +2731,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -2763,10 +2763,10 @@
         <v>1</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J24" t="s">
         <v>68</v>
@@ -2801,10 +2801,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J25" t="s">
         <v>101</v>
@@ -2845,10 +2845,10 @@
         <v>1</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J26" t="s">
         <v>115</v>
@@ -2889,10 +2889,10 @@
         <v>1</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L27" s="14"/>
       <c r="N27" t="s">
@@ -2922,10 +2922,10 @@
         <v>1</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L28" s="14"/>
     </row>
@@ -2952,10 +2952,10 @@
         <v>1</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>117</v>
@@ -2987,7 +2987,7 @@
         <v>85</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J30" t="s">
         <v>118</v>
@@ -3010,7 +3010,7 @@
         <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D31" t="s">
         <v>59</v>
@@ -3025,10 +3025,10 @@
         <v>1</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L31" s="14"/>
     </row>
